--- a/sources/trueogre_step8.xlsx
+++ b/sources/trueogre_step8.xlsx
@@ -7992,12 +7992,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">

--- a/sources/trueogre_step8.xlsx
+++ b/sources/trueogre_step8.xlsx
@@ -851,6 +851,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
@@ -913,6 +918,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
@@ -973,6 +983,11 @@
       <c r="U8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1099d7d4-6a6d-45ae-81cf-93df73c48ae4</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">

--- a/sources/trueogre_step8.xlsx
+++ b/sources/trueogre_step8.xlsx
@@ -417,37 +417,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB103"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col hidden="1" min="4" max="4"/>
-    <col width="85" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col hidden="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="47" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="37" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="37" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col hidden="1" min="16" max="16"/>
-    <col width="37" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="115" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col hidden="1" min="5" max="5"/>
+    <col width="85" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col hidden="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="47" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col width="37" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col hidden="1" min="17" max="17"/>
+    <col width="37" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="115" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
     <col width="38" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,125 +476,130 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -610,57 +616,57 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Body Slam</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Body Slam</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>d97c2564-42c8-4172-8677-d37f5333dcab</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>cdaa5de9-d503-4d4b-abcc-68f295d1457e</t>
         </is>
@@ -677,57 +683,57 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Bear Hug</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Bear Hug</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>bd062463-8eb8-4aa3-9b97-be963b994439</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>f4434270-bf4d-42b5-aced-5a6f8d537ec3</t>
         </is>
@@ -744,57 +750,57 @@
           <t>df,DF+2+4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Waning Moon</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Waning Moon</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>29c78b85-aab0-4c9c-a706-ae3985be2571</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>b9e51cf0-ef80-443c-bd37-2b6ee9b26653</t>
         </is>
@@ -818,50 +824,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Choke Slam</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Choke Slam</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>10,15,25</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>10,15,25</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -885,50 +896,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Rag Doll</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Rag Doll</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -952,50 +968,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Bear Swing</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Bear Swing</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1099d7d4-6a6d-45ae-81cf-93df73c48ae4</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>1099d7d4-6a6d-45ae-81cf-93df73c48ae4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1027,125 +1048,130 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="Q11" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R11" s="1" t="inlineStr">
+      <c r="S11" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S11" s="1" t="inlineStr">
+      <c r="T11" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T11" s="1" t="inlineStr">
+      <c r="U11" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U11" s="1" t="inlineStr">
+      <c r="V11" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V11" s="1" t="inlineStr">
+      <c r="W11" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
+      <c r="X11" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X11" s="1" t="inlineStr">
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AA11" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
+      <c r="AC11" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1162,77 +1188,77 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>a4672226-891f-4441-af4b-7a3e21ffaf6f</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>109d46b8-be6b-4d89-906b-81c40eb4ec8f</t>
         </is>
@@ -1249,77 +1275,77 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>fdd1207f-0f08-489f-a669-74af720773fc</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>a5b9fa7b-dd75-406f-9614-84302bb9676a</t>
         </is>
@@ -1336,77 +1362,77 @@
           <t>3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>707ac401-93e5-4f81-883c-02480bb5c45c</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>1d3fe2df-a50e-485a-9c44-8bd0e9ee7e6b</t>
         </is>
@@ -1423,31 +1449,26 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1465,35 +1486,40 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>93db2e9d-77fb-4304-a27c-3d22bc4e74b4</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>db6fff26-83be-4b9f-a2c0-aeab0efdcd4b</t>
         </is>
@@ -1510,77 +1536,77 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>b6039281-cc1c-4343-a18a-cdb002f7d600</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>5cedb419-8ab4-4c99-86d6-fc038f5f14c7</t>
         </is>
@@ -1597,31 +1623,26 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1639,35 +1660,40 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>63ad818e-9759-4c62-9a4b-6eabb86c4031</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>45bd705f-24c9-4589-ae00-cabf1dc8e61b</t>
         </is>
@@ -1684,77 +1710,77 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>cc20bd65-792e-40bc-9b3f-a7db5b358feb</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>1d76bb9c-0fc7-4163-a532-01d12c629e98</t>
         </is>
@@ -1771,31 +1797,26 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>KD</t>
@@ -1813,35 +1834,40 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>2a0c77a9-4306-4fa8-b070-82da6e25f62b</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>cb82377f-2117-4f33-9762-eaf6c222f43a</t>
         </is>
@@ -1858,77 +1884,77 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>93cc65da-41fd-400b-87fb-48987143e85d</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>9851d122-6a58-4886-815b-c28675bb7309</t>
         </is>
@@ -1945,77 +1971,77 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>a9024b86-9bfa-41ca-9632-2e7311c6b2f4</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>986fbe5a-ebe9-4a5b-80b5-8e25b43dc74e</t>
         </is>
@@ -2032,77 +2058,77 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>6d59a460-3e32-4717-a605-369ff9446af9</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>2c9a243f-616b-4e3f-a42e-2ae1564e45e9</t>
         </is>
@@ -2119,77 +2145,77 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-12</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>29cd9af7-cd5f-4c96-9ad4-436425ed261d</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>1da2c7df-4884-47e7-ab59-408882142590</t>
         </is>
@@ -2206,77 +2232,77 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>69162119-045d-491e-bf78-9b8b9d957e8f</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>ff31166e-4bf7-4695-b86c-703d5419a7c8</t>
         </is>
@@ -2293,77 +2319,77 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>b5895748-8bd0-45af-b343-cd578c656963</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>a2a229a5-f1e1-4906-95d0-889764fcdb9d</t>
         </is>
@@ -2380,77 +2406,77 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>6ca7e32f-4200-4e77-bc6c-7a9599e46258</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>66972deb-6e76-4527-89d0-832c76591d4c</t>
         </is>
@@ -2467,77 +2493,77 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>9e98aa11-1900-438b-9ca5-df7a466fb2b3</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>aa5294b8-715d-472d-a792-5e8b69ae89f4</t>
         </is>
@@ -2554,77 +2580,77 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>be151f58-3c0a-4c39-8043-6b12aef96c98</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>260ba78d-f8ca-4eed-aba5-ce89f22627a5</t>
         </is>
@@ -2641,31 +2667,26 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>KD</t>
@@ -2683,35 +2704,40 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>34950f8a-ac92-4391-8e4d-6af8df56e806</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>ac13e798-11f8-4798-9539-6de23dd95658</t>
         </is>
@@ -2728,77 +2754,77 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>-21</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>a0b702df-a682-4880-bd5c-c2361c398b4c</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>bbaaf973-768d-4577-b0a5-769a21d21a59</t>
         </is>
@@ -2815,77 +2841,77 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>53db1f13-a11e-4e73-aa5b-9f2a41e9ccc0</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>a2053c8e-7406-4e0e-bfd7-be7fbf17de89</t>
         </is>
@@ -2902,77 +2928,77 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>+8</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>3b82365c-ef66-45a6-b147-4b0d5e4eed18</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>a04cff42-4659-44d6-99e0-374c5c751814</t>
         </is>
@@ -2989,77 +3015,77 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>64489914-557c-4db3-83b2-5d1435732c91</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>136ff860-c104-422a-8e4e-2331ddd9fe86</t>
         </is>
@@ -3076,77 +3102,77 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>1cf55052-4024-4952-b377-790187d1679c</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>1d22909e-7672-4a37-a404-67dbbe023fc5</t>
         </is>
@@ -3163,77 +3189,77 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>eaec32bd-f891-4de6-a435-266f34a85d3b</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>65955214-865f-4697-a2f1-c133c71f3f67</t>
         </is>
@@ -3265,125 +3291,130 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="I38" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr">
+      <c r="K38" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K38" s="1" t="inlineStr">
+      <c r="L38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
+      <c r="M38" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M38" s="1" t="inlineStr">
+      <c r="N38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N38" s="1" t="inlineStr">
+      <c r="O38" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O38" s="1" t="inlineStr">
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="Q38" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q38" s="1" t="inlineStr">
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R38" s="1" t="inlineStr">
+      <c r="S38" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S38" s="1" t="inlineStr">
+      <c r="T38" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T38" s="1" t="inlineStr">
+      <c r="U38" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U38" s="1" t="inlineStr">
+      <c r="V38" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V38" s="1" t="inlineStr">
+      <c r="W38" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
+      <c r="X38" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
+      <c r="Y38" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB38" s="1" t="inlineStr">
+      <c r="AC38" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3400,47 +3431,47 @@
           <t>1&lt;2</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Double Punch</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>13ba56df-72a7-48eb-a224-25be9adaa87e</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>3a8950a3-c685-4346-b3bb-3b0ee796c739</t>
         </is>
@@ -3457,87 +3488,87 @@
           <t>1&lt;2,2</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Demon Slayer</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>-5 -6 -8</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>-5 -6 -8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>+3 +3 +1</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>+3 +3 +1</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>+6 +3 +1</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>+6 +3 +1</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>5,15,18</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>5,15,18</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>hhh</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>45428de1-032c-42ee-86b0-b36fbdc8009c</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>d17eac4a-6179-4d34-92c5-efb1bb6f5b02</t>
         </is>
@@ -3554,87 +3585,87 @@
           <t>df+1,2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Double Face Buster</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Double Face Buster</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>-3 -6</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>-3 -6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+8 +5</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>16,10</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>16,10</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>074dac01-4547-4be1-8ab5-a76903781603</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>e5299c2d-8bdd-4930-bb72-4b507291e752</t>
         </is>
@@ -3651,87 +3682,87 @@
           <t>1,1&lt;2</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Shining Fists</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>-5 -6 -14</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>-5 -6 -14</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>+3 +2 KD</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>+3 +2 KD</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+6 +2 KD</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>+6 +2 KD</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>5,8,15</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>5,8,15</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>87dd4c43-5799-42f7-8297-10b2ee7369be</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>c26c8511-dbe1-418c-9c44-2da1759866af</t>
         </is>
@@ -3748,41 +3779,36 @@
           <t>D,f+1</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Cat Thrust</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Cat Thrust</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3800,40 +3826,45 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>8bdea779-3bda-4752-8310-fdac2942c6ab</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>933315eb-2d4f-42f9-9fe5-a502bf964e1b</t>
         </is>
@@ -3850,41 +3881,36 @@
           <t>f,f+1+2</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Lunging Double Fist</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Lunging Double Fist</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3902,35 +3928,40 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>3a5b97db-c3c2-429a-af91-60fc0a98d188</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>1236da04-86c7-46c8-9eb6-a629729abea9</t>
         </is>
@@ -3947,41 +3978,36 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Buffalo Horn</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Buffalo Horn</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>KD</t>
@@ -3999,40 +4025,45 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>0000302f-b6ae-4c5f-91bf-f807c6dcad6a</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>9e2ca927-e1b4-493e-a431-d4714644c69d</t>
         </is>
@@ -4049,41 +4080,36 @@
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Black Shoulder</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Black Shoulder</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4101,40 +4127,45 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>aefab9c2-2f40-4531-b5fa-48ec1f239e87</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>6c29764d-68e3-4eba-b2f9-6e81d54fab89</t>
         </is>
@@ -4151,41 +4182,36 @@
           <t>uf+1+2</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Knuckle Bomb</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4203,35 +4229,40 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>c96ea765-2bfb-43d7-8333-139abfab087a</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>b75efbab-53c3-4a65-9633-fca5467d0324</t>
         </is>
@@ -4248,41 +4279,36 @@
           <t>uf,N+1+2</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Jumping Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Jumping Knuckle Bomb</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4300,35 +4326,40 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>1da753ae-26f9-4a72-ba24-6f38ffa68a90</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>1f84dffa-0dfb-4715-810c-5930195a225e</t>
         </is>
@@ -4345,87 +4376,87 @@
           <t>2,2</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Demon Backhand Spin</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>-2 -13</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>-2 -13</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+7 +2</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>12,21</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>5b11382b-cfc2-4248-90fe-f116ffb8f7d9</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>2fb2759a-3639-4d3a-b161-3d96bc680a7f</t>
         </is>
@@ -4442,41 +4473,36 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Demon Gut Punch</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Demon Gut Punch</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4494,40 +4520,45 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>27b074fd-f015-4301-8a5d-93e2619dce3c</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>fdfcceef-4bbd-4868-b97f-570f8ef67202</t>
         </is>
@@ -4544,41 +4575,36 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Front Strike</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Front Strike</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4596,35 +4622,40 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>17146bdb-f211-4471-937a-c136c307f399</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>dfcfde61-ff60-4e03-90fe-7008cf52e828</t>
         </is>
@@ -4641,92 +4672,92 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Upper</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>+24</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>JGc SH</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>ad9a2193-0759-4110-b02d-0bea103ece98</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>c7f0d7f7-9bbc-49a3-8987-2871684a4f97</t>
         </is>
@@ -4743,51 +4774,46 @@
           <t>D,f+2</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Scarlett Windmill</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Scarlett Windmill</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>-26</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>-26</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4795,40 +4821,45 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>7a6fd7ac-6a38-4a7d-aca1-669f3842300b</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>db3857ee-8361-4ffe-ab32-e14d8a4cc319</t>
         </is>
@@ -4845,41 +4876,36 @@
           <t>D,df+2</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Scarlet Sweep</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Scarlet Sweep</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4897,40 +4923,45 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>3d6e287f-4f76-4512-bfc2-22bd430e39d1</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>9c886bb5-5f96-4daa-b9c3-a493c1b1a326</t>
         </is>
@@ -4947,41 +4978,36 @@
           <t>f,f+3</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Split Axe Kick</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>KD</t>
@@ -4999,35 +5025,40 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>4d16ea25-0e0d-493e-9acb-4084d3db8b56</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>63865994-eefd-4d6c-9968-1f1567395807</t>
         </is>
@@ -5044,41 +5075,36 @@
           <t>ub+3</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Back Flip Kick</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Back Flip Kick</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>-22</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>KD</t>
@@ -5096,35 +5122,40 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>bc8715f4-ee25-4939-a0fe-17d2dfe68398</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>9a17b478-d153-4e7d-aa82-425d7f2fe196</t>
         </is>
@@ -5141,97 +5172,97 @@
           <t>ub+3,2</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>– Tooth Fairy</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Back Flip Kick – Tooth Fairy</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>-22 -18</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>20,25</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>ced9a85f-14c1-4b54-979c-576f60c45b13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>ca0a1a74-8ec9-449b-9485-d88f68562e85</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>bc8715f4-ee25-4939-a0fe-17d2dfe68398</t>
         </is>
@@ -5248,97 +5279,97 @@
           <t>uf+3,4,3</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Hunting Hawk</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Hunting Hawk</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>27 x x</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>27 x x</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>-6 +7 x</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>-6 +7 x</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>KD KD KD</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>x KD KD</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>x KD KD</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>15,14,25</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>15,14,25</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>If the 1st hit is blocked the 3rd hit is cancelled. If the first hit whiffs the string ends.</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>1c62d1bd-3d08-45f5-ac71-164e00a1130c</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>49b01202-b03c-4a46-8207-765752d740ef</t>
         </is>
@@ -5355,92 +5386,92 @@
           <t>FC+3,3,d+3</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Snake Creep</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Snake Creep</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>-14 -19 -17</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>-14 -19 -17</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>-3 -9 -3</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>12,19,7</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>12,19,7</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>LLL</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>b6775f91-b6c1-48d2-b81e-aa9c1e17f3a6</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>046f19da-2710-44df-bca3-8c2315921250</t>
         </is>
@@ -5457,97 +5488,97 @@
           <t>FC+3,3,N+3</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Snake Blade</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Snake Blade</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>-14 -19 -15</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>-14 -19 -15</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>-3 -9 KD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>12,19,25</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>12,19,25</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>LLm</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>LLm</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>f05d113c-7118-40e8-811a-b3c8858cb6db</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>bfdb914a-9bd3-4a99-b413-05bc15a64bbe</t>
         </is>
@@ -5564,87 +5595,87 @@
           <t>WS+3,3</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>-19 -19</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>-19 -19</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>-8 -8</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>d012b447-8715-49e6-9958-d6befbfddb6c</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>66b01ad7-cdf5-4c87-8dda-a0351cb684d5</t>
         </is>
@@ -5661,92 +5692,92 @@
           <t>WS+3,3,df+3</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>– Step In Kick Infinite Starter</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Tsunami Kick – Step In Kick Infinite Starter</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>-19 -19 -14</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>-8 -8 -3</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>-8 -8 -3</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>10,25,15</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>The Infinite Kicks have to be started with 1 Silver Low or 1 Step In Kick after the WS+3,3.</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>9a30e85f-ca52-4df4-931d-6a6d9e517809</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>0403f41e-a1c2-4726-acc5-e57484f2c9aa</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>d012b447-8715-49e6-9958-d6befbfddb6c</t>
         </is>
@@ -5763,92 +5794,92 @@
           <t>WS+3,3,D+3</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>– Silver Low Infinite Starter</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>-19 -19 -19</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>-8 -8 -8</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>-8 -8 -8</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>10,25,15</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>mml</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>The Infinite Kicks have to be started with 1 Silver Low or 1 Step In Kick after the WS+3,3.</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>9b93f0fa-f96d-49c1-92eb-569bd6922d8d</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>71ca4ed1-01a6-4d15-ab22-be5ea335e6fe</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>d012b447-8715-49e6-9958-d6befbfddb6c</t>
         </is>
@@ -5865,92 +5896,92 @@
           <t>WS+3,3,D+3,3,3,3,3...</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>–– Rave Kicks</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>-19 -16 -19 -16...</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>-19 -19 -19 -19 -16 -19 -16...</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>-8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5...</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>10,10,10,10...</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>10,10,10,10...</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>10,25,15,10,10,10,10...</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>mhmh</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>mmlmhmh</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>0db55ab2-9aa6-4687-bab3-da30609a62ec</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>c410bafc-1f2f-4a1e-962e-775fbfb6f35c</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>9b93f0fa-f96d-49c1-92eb-569bd6922d8d</t>
         </is>
@@ -5967,92 +5998,92 @@
           <t>WS+3,3,D+3,3,3,3,3...,u+3,3,3...</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>––– Feint Hammer - Rave Kicks</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Feint Hammer - Rave Kicks</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>-19 -16 -19...</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>-19 -19 -19 -19 -16 -19 -16... -19 -16 -19...</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>10,25,15,10,10,10,10...,15,10,10...</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>mmh</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>mmlmhmhmmh</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>f1b78600-16c3-4da0-bb95-1b8ebcca3657</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>1ac7e5da-f6c4-447a-9f1b-50ffdc63d142</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>0db55ab2-9aa6-4687-bab3-da30609a62ec</t>
         </is>
@@ -6069,92 +6100,92 @@
           <t>WS+3,3,D+3,3,3,3,3...,d+3,3,3...</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>––– Silver Low - Rave Kicks</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Silver Low - Rave Kicks</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>-19 -16 -19...</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>-19 -19 -19 -19 -16 -19 -16... -19 -16 -19...</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>-8 -5 -8...</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>-8 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>15,10,10...</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>10,25,15,10,10,10,10...,15,10,10...</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>lmh</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>mmlmhmhlmh</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>2713dd4e-0b81-4ff8-bcf2-00e6585a4446</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>d0245fff-f2e9-4e2b-8396-aaffc9c58dc6</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>0db55ab2-9aa6-4687-bab3-da30609a62ec</t>
         </is>
@@ -6171,31 +6202,26 @@
           <t>f,f+3+4</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Exploder</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Exploder</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6213,40 +6239,45 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>d447b79d-6c4f-4921-b0f3-ec76217d8cd3</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>4bab5ba5-d69c-4cb5-9fa9-973c2f8b3ac6</t>
         </is>
@@ -6263,31 +6294,26 @@
           <t>f,f,N+3+4</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Delayed Dragon Slide</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Delayed Dragon Slide</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6305,35 +6331,40 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>1e76e7a6-586b-492c-8970-7f04932deb6a</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>70d0d481-c242-4070-98b7-a5afc5f845ef</t>
         </is>
@@ -6350,41 +6381,36 @@
           <t>WS+3+4</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Spin Kick</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Spin Kick</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6402,35 +6428,40 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>657308b9-36ca-4bf8-8d9e-0c2ab76020d4</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>eecc8540-e838-401b-a0a8-af7919d7e02a</t>
         </is>
@@ -6447,92 +6478,92 @@
           <t>u+3+4</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Evil Wheel</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Evil Wheel</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>8c21f7f4-2a95-4f73-aad8-69f9292aa2b6</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>6720feff-3e69-4c9b-ab8a-b93ae9878e25</t>
         </is>
@@ -6549,41 +6580,36 @@
           <t>d+3+4</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Demon Tail</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Demon Tail</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6601,40 +6627,45 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>b5080deb-3130-4686-b8ff-cbd3681e48bc</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>cb037c78-beef-41ef-82b3-413aa59d1862</t>
         </is>
@@ -6651,41 +6682,36 @@
           <t>df+3+4</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Tail Spin</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Tail Spin</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6703,35 +6729,40 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>dea1f32a-8964-4427-bea9-f6e215a69702</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>a8527366-c456-48d0-9f62-7078c3b10974</t>
         </is>
@@ -6748,92 +6779,92 @@
           <t>df+3+4~DF</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>– Back Turned Position</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Tail Spin – Back Turned Position</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>-7 -10</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>25,-</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>m-</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>BT</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>9eefea67-aa53-4e1a-aaca-6f29e56afa99</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>093f8234-1ce7-4839-b64d-3b9bb4a117ea</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>dea1f32a-8964-4427-bea9-f6e215a69702</t>
         </is>
@@ -6850,87 +6881,87 @@
           <t>df+3+4,3+4</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>– Double Spin</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Tail Spin – Double Spin</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>-7 -3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>25,25</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="T74" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>e0bea66c-b912-48a4-bff8-b4d5a39dac3b</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>59e67342-ee23-4345-9080-e75f9e85b1f9</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>dea1f32a-8964-4427-bea9-f6e215a69702</t>
         </is>
@@ -6947,41 +6978,36 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Axe Kick</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>KD</t>
@@ -6999,40 +7025,45 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>KSco GB</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>4974fbc2-20b0-44e1-8e65-27c331158953</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>ad82fc77-af35-429f-8673-32dc8b1f7e4c</t>
         </is>
@@ -7049,41 +7080,36 @@
           <t>SS+4</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Azteca Shoot</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Azteca Shoot</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7101,40 +7127,45 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>4cbb4e08-c40a-4812-bfa3-0e54406c81f3</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>cb8dcfa6-afc7-4439-8989-df044077b09a</t>
         </is>
@@ -7151,41 +7182,36 @@
           <t>d,db+4</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Blazing Kick</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Blazing Kick</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7203,45 +7229,50 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>04f19edf-fc75-4fa8-a535-0615691e9da0</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>dfae095f-99b9-447f-b09d-d61f23c9f57f</t>
         </is>
@@ -7258,87 +7289,87 @@
           <t>d+4,N+4</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Laser Edge - Machine Gun Kick</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Laser Edge - Machine Gun Kick</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>-11 -9</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>-11 -9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>-12 0</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>-12 0</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>7,20</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>7,20</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>lh</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="T78" t="inlineStr">
         <is>
           <t>lh</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>fbfac625-1433-4147-8f3d-7211675675a3</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>a71bce17-59a3-4abe-b4be-012dafe81ca6</t>
         </is>
@@ -7355,41 +7386,36 @@
           <t>f,f+4</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Bazooka Kick</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Bazooka Kick</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7407,40 +7433,45 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="T79" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>c3e081e8-75f8-424d-b71a-80e23c4db276</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>2b9d55d4-f3ae-492b-9e3b-a3fca6a4f0f3</t>
         </is>
@@ -7457,41 +7488,36 @@
           <t>f,f,N+4</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Hammer Heel</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Hammer Heel</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7509,35 +7535,40 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>4c05ca0e-e3f9-4d53-bd3b-533e9320a472</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>6bb0bef4-f43c-4c17-9cd1-a153b50d4932</t>
         </is>
@@ -7554,87 +7585,87 @@
           <t>WS+4,4</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Tsunami Kick</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>-3 -15</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>+8 -4</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>KD KD</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>13,18</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>13,18</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>b15bba76-e409-4a1d-9214-1426450edd84</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>4ea0192d-48d1-48ed-8a54-7826295c5cc3</t>
         </is>
@@ -7651,31 +7682,26 @@
           <t>4~3</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Scissors Kick</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Scissors Kick</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7693,35 +7719,40 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="R82" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>e464b85d-d543-473f-a12c-b291b910af4a</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>dcadda30-29db-4d01-b00d-ca9bf98735b5</t>
         </is>
@@ -7738,52 +7769,52 @@
           <t>DF</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Deadly Feast</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Deadly Feast</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>Low and Mid Punch Reversal. Reversal can be escaped with 1+2..</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>42de9619-c860-4f8a-a9ec-46593608f839</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>9771b599-54cd-42a8-ae40-4808965418c6</t>
         </is>
@@ -7815,125 +7846,130 @@
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E86" s="1" t="inlineStr">
+      <c r="F86" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
+      <c r="H86" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H86" s="1" t="inlineStr">
+      <c r="I86" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I86" s="1" t="inlineStr">
+      <c r="J86" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J86" s="1" t="inlineStr">
+      <c r="K86" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K86" s="1" t="inlineStr">
+      <c r="L86" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L86" s="1" t="inlineStr">
+      <c r="M86" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M86" s="1" t="inlineStr">
+      <c r="N86" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N86" s="1" t="inlineStr">
+      <c r="O86" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O86" s="1" t="inlineStr">
+      <c r="P86" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P86" s="1" t="inlineStr">
+      <c r="Q86" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q86" s="1" t="inlineStr">
+      <c r="R86" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R86" s="1" t="inlineStr">
+      <c r="S86" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S86" s="1" t="inlineStr">
+      <c r="T86" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T86" s="1" t="inlineStr">
+      <c r="U86" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U86" s="1" t="inlineStr">
+      <c r="V86" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V86" s="1" t="inlineStr">
+      <c r="W86" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W86" s="1" t="inlineStr">
+      <c r="X86" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X86" s="1" t="inlineStr">
+      <c r="Y86" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y86" s="1" t="inlineStr">
+      <c r="Z86" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z86" s="1" t="inlineStr">
+      <c r="AA86" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA86" s="1" t="inlineStr">
+      <c r="AB86" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB86" s="1" t="inlineStr">
+      <c r="AC86" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7950,31 +7986,26 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Hell Flame</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Hell Flame</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>KD</t>
@@ -7992,45 +8023,50 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="W87" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>Bryan, Gun Jack, Jack 2 and Prototype Jack only stagger upon hitting, they do not fall to the ground.</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>5becde5d-2a0b-44d4-839a-b9198e2dc9b6</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>acee6546-66c4-4fe1-a0b5-c4ea0ae24d36</t>
         </is>
@@ -8047,31 +8083,26 @@
           <t>d+1+2</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Hell Inferno</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Hell Inferno</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8089,35 +8120,40 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="W88" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>Bryan, Gun Jack, Jack 2 and Prototype Jack only stagger upon hitting, they do not fall to the ground.</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>59f0bd3d-1523-4899-90d8-36636baaf8b3</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>8288c775-4d30-4001-827e-2bbc50a75248</t>
         </is>
@@ -8141,29 +8177,29 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>KND 3+4</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Owl's Hunt</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Owl's Hunt</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8181,25 +8217,30 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>5a1796e9-5c18-4682-a077-f05dbb8d8945</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>746e824f-cd21-4185-9f66-1fd501f18795</t>
         </is>
@@ -8216,57 +8257,57 @@
           <t>PLD 3+4~f</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>– Warp Behind</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Owl's Hunt – Warp Behind</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>40,40</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>3540e3c4-c6fb-4f45-9e04-23918c09551f</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>56538f11-79c5-46bb-9916-e26a83c786af</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>5a1796e9-5c18-4682-a077-f05dbb8d8945</t>
         </is>
@@ -8283,57 +8324,57 @@
           <t>PLD 3+4~u</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>– Side Warp</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Owl's Hunt – Side Warp</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>40,40</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>60741d7f-b99e-4c6c-a67d-d75af83e117a</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>cc90d112-c1a2-4362-aa47-3d5b41d1fe8b</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>5a1796e9-5c18-4682-a077-f05dbb8d8945</t>
         </is>
@@ -8350,57 +8391,57 @@
           <t>PLD 3+4~d</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>– Side Warp</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Owl's Hunt – Side Warp</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>40,40</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>a0671fec-f64b-4a0c-a1bc-c79fad18ed4a</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>b3c95097-d18d-460e-bad7-7bd31001cd7c</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>5a1796e9-5c18-4682-a077-f05dbb8d8945</t>
         </is>
@@ -8417,31 +8458,26 @@
           <t>db+1+2</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Bloody Scissors</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Bloody Scissors</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8459,40 +8495,45 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
+      <c r="W93" t="inlineStr">
         <is>
           <t>CF JG</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>29e2d1c0-23fd-430a-bcd3-bbf19a5fb2cf</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>9ba7b8e6-5901-4f73-9b40-5513f25ff564</t>
         </is>
@@ -8516,29 +8557,29 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>uf+1+2~D</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8556,35 +8597,40 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
+      <c r="T94" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>1a3443f3-19f0-43a5-beb1-4f35c4a9e45a</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>6a386170-8928-4451-9337-124aa9f521b4</t>
         </is>
@@ -8608,29 +8654,29 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>uf,N+1+2~D</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>Jump In Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Jump In Burning Knuckle Bomb</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8648,35 +8694,40 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>71c5e3dc-f280-49e8-853e-d0c5b9e1c4c7</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>294c9753-233e-405c-ad6e-caa7aca64c12</t>
         </is>
@@ -8693,31 +8744,26 @@
           <t>b,b+1+2</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Indigo Punch</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Indigo Punch</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8735,35 +8781,40 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>19c0cda3-6ce0-41de-898b-605b0f9d3d85</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>19f53d6a-0f04-4100-8444-cb40320e6af3</t>
         </is>
@@ -8780,31 +8831,26 @@
           <t>f,f+2</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Deadly Spear</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Deadly Spear</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8822,45 +8868,50 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
           <t>15,20</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>15,20</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>CF JG</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>After blocking the 1st hit, the unblockable hit can be avoided by a SS or Back Dash.</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>538525af-a899-48e0-acbc-93fc0de46269</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>a714dbe1-fe16-4eb8-88fb-66f4fb8b1532</t>
         </is>
@@ -8877,31 +8928,26 @@
           <t>b+2</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Kunai Stab</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Kunai Stab</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>KD</t>
@@ -8919,40 +8965,45 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="R98" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="W98" t="inlineStr">
         <is>
           <t>CF JG</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>e6a2f031-0520-43fa-9506-a84f821ad809</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>da3e17f0-ee35-46d7-b130-0947f170115c</t>
         </is>
@@ -8969,31 +9020,26 @@
           <t>f,f,N+2</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Kunai Advance</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Kunai Advance</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>KD</t>
@@ -9011,40 +9057,45 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="R99" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="T99" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="W99" t="inlineStr">
         <is>
           <t>CF JG</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>dc0b1830-7ac7-41a3-91d9-3e5a2429ff9f</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>d020ac60-c41a-4f34-affd-426781f973fc</t>
         </is>
@@ -9061,31 +9112,26 @@
           <t>b+2+3</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Sidewinder</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Sidewinder</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>KD</t>
@@ -9103,35 +9149,40 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>a325aa01-c136-4962-81e1-43d88a5a6e99</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>7e11ef87-5bbf-4af1-92bc-ccc7db9e5b34</t>
         </is>
@@ -9163,125 +9214,130 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E103" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H103" s="1" t="inlineStr">
+      <c r="I103" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I103" s="1" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J103" s="1" t="inlineStr">
+      <c r="K103" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K103" s="1" t="inlineStr">
+      <c r="L103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L103" s="1" t="inlineStr">
+      <c r="M103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M103" s="1" t="inlineStr">
+      <c r="N103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N103" s="1" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O103" s="1" t="inlineStr">
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P103" s="1" t="inlineStr">
+      <c r="Q103" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q103" s="1" t="inlineStr">
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R103" s="1" t="inlineStr">
+      <c r="S103" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S103" s="1" t="inlineStr">
+      <c r="T103" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T103" s="1" t="inlineStr">
+      <c r="U103" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U103" s="1" t="inlineStr">
+      <c r="V103" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V103" s="1" t="inlineStr">
+      <c r="W103" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W103" s="1" t="inlineStr">
+      <c r="X103" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X103" s="1" t="inlineStr">
+      <c r="Y103" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z103" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA103" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB103" s="1" t="inlineStr">
+      <c r="AC103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
